--- a/wooclap/imports/optional/06_Constraints_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/06_Constraints_Part_2_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$2</definedName>

--- a/wooclap/imports/optional/06_Constraints_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/06_Constraints_Part_2_optional.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L02-O03 · Why might you restart a local search from a different initial timetable?</t>
+          <t>L02-O03 · A local-search candidate has 1 conflict. Every one-variable neighbor has at least 1. One neighbor also has 1 conflict, and from it a move reaches 0. Which conclusion follows for strict improvement, which accepts only lower scores?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -527,22 +527,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Every restart guarantees a valid timetable.</t>
+          <t>Strict improvement takes the equal-score move, then reaches 0.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A different starting point may lead to a better result.</t>
+          <t>Strict improvement stops here; allowing the equal-score move could reach a solution in two steps.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The rules of the problem stop applying after a restart.</t>
+          <t>The current candidate is globally optimal because no immediate move improves it.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>All starting points must produce the same sequence of changes.</t>
+          <t>A restart is guaranteed to reach the zero-conflict candidate on its next move.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
